--- a/ekspor-xlsx/sac/kota_asean_kualitas_udara.xlsx
+++ b/ekspor-xlsx/sac/kota_asean_kualitas_udara.xlsx
@@ -430,20 +430,20 @@
   <dimension ref="A1:H623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>negara</t>
+          <t>country</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -453,32 +453,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>kota</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tahun</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>polutan</t>
+          <t>pollutant</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>konsentrasi_ug_m3</t>
+          <t>concentration_ug_m3</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>cakupan_waktu_persen</t>
+          <t>temporal_coverage_percent</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>jenis_stasiun</t>
+          <t>station_type</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1365,7 +1365,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2049,7 +2049,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3253,7 +3253,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4655,7 +4655,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4685,7 +4685,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4715,7 +4715,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4745,7 +4745,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5455,7 +5455,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5515,7 +5515,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5545,7 +5545,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5635,7 +5635,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6411,7 +6411,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6441,7 +6441,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7083,7 +7083,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7113,7 +7113,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7143,7 +7143,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7173,7 +7173,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7203,7 +7203,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7233,7 +7233,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7265,7 +7265,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7295,7 +7295,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7325,7 +7325,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7415,7 +7415,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7703,7 +7703,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7733,7 +7733,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -9099,7 +9099,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -9129,7 +9129,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -9561,7 +9561,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9591,7 +9591,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -10581,7 +10581,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -10611,7 +10611,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -10929,7 +10929,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -10959,7 +10959,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10989,7 +10989,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -11019,7 +11019,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -11049,7 +11049,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -11871,7 +11871,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -11901,7 +11901,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -11931,7 +11931,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -11961,7 +11961,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -12021,7 +12021,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -12823,7 +12823,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -12853,7 +12853,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -13051,7 +13051,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -13081,7 +13081,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -13111,7 +13111,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -13141,7 +13141,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -13261,7 +13261,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -13291,7 +13291,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -13471,7 +13471,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -14423,7 +14423,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -14453,7 +14453,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -15331,7 +15331,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16109,7 +16109,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16139,7 +16139,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16169,7 +16169,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16199,7 +16199,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16229,7 +16229,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16259,7 +16259,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16289,7 +16289,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16321,7 +16321,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -16353,7 +16353,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -16385,7 +16385,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -16417,7 +16417,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -16449,7 +16449,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -16481,7 +16481,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -16513,7 +16513,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -16545,7 +16545,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -16575,7 +16575,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -16605,7 +16605,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -16637,7 +16637,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -16669,7 +16669,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -16701,7 +16701,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -16733,7 +16733,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -16765,7 +16765,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -16797,7 +16797,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -16829,7 +16829,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -16861,7 +16861,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -16893,7 +16893,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -16925,7 +16925,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -16957,7 +16957,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -16989,7 +16989,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17021,7 +17021,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17053,7 +17053,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17087,7 +17087,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17121,7 +17121,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Singapura</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -18057,7 +18057,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -18087,7 +18087,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -18117,7 +18117,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -18147,7 +18147,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -18585,7 +18585,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18615,7 +18615,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -18645,7 +18645,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18675,7 +18675,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18705,7 +18705,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18735,7 +18735,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18861,7 +18861,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18891,7 +18891,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -19397,7 +19397,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -19535,7 +19535,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -20847,7 +20847,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
